--- a/workshop_registration_form_templates/033_young_engineers_event_registration--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/033_young_engineers_event_registration--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>session_start</t>
+          <t>session_start_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Session Start</t>
+          <t>Session Start 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>session_end</t>
+          <t>session_end_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Session End</t>
+          <t>Session End 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>session_duration</t>
+          <t>session_duration_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>session_choices</t>
+          <t>session_choices_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Session Choices</t>
+          <t>Session Choices 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>session_choices_choices</t>
+          <t>session_choices_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>session_choices_choices</t>
+          <t>session_choices_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
